--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_19-01-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_19-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="137">
   <si>
     <t>SKU</t>
   </si>
@@ -224,42 +224,6 @@
   </si>
   <si>
     <t>POA</t>
-  </si>
-  <si>
-    <t>£27.48 (Was £32.98)</t>
-  </si>
-  <si>
-    <t>£34.23 (Was £41.07)</t>
-  </si>
-  <si>
-    <t>£39.53 (Was £47.43)</t>
-  </si>
-  <si>
-    <t>£41.33 (Was £49.60)</t>
-  </si>
-  <si>
-    <t>£45.39 (Was £54.47)</t>
-  </si>
-  <si>
-    <t>£49.14 (Was £58.97)</t>
-  </si>
-  <si>
-    <t>£31.66 (Was £37.99)</t>
-  </si>
-  <si>
-    <t>£63.71 (Was £76.45)</t>
-  </si>
-  <si>
-    <t>£62.80 (Was £75.36)</t>
-  </si>
-  <si>
-    <t>£71.35 (Was £85.62)</t>
-  </si>
-  <si>
-    <t>£75.80 (Was £90.96)</t>
-  </si>
-  <si>
-    <t>£77.34 (Was £92.81)</t>
   </si>
   <si>
     <t>£11.97</t>
@@ -888,25 +852,25 @@
         <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="K2" t="s">
         <v>69</v>
       </c>
       <c r="L2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="M2" t="s">
         <v>69</v>
       </c>
       <c r="N2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -932,13 +896,13 @@
         <v>69</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K3" t="s">
         <v>69</v>
@@ -950,7 +914,7 @@
         <v>69</v>
       </c>
       <c r="N3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -976,13 +940,13 @@
         <v>69</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="K4" t="s">
         <v>69</v>
@@ -994,7 +958,7 @@
         <v>69</v>
       </c>
       <c r="N4" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1017,16 +981,16 @@
         <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="K5" t="s">
         <v>69</v>
@@ -1038,7 +1002,7 @@
         <v>69</v>
       </c>
       <c r="N5" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1061,16 +1025,16 @@
         <v>48</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s">
         <v>69</v>
@@ -1082,7 +1046,7 @@
         <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1105,16 +1069,16 @@
         <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="K7" t="s">
         <v>69</v>
@@ -1126,7 +1090,7 @@
         <v>69</v>
       </c>
       <c r="N7" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1149,28 +1113,28 @@
         <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="J8" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="K8" t="s">
         <v>69</v>
       </c>
       <c r="L8" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="M8" t="s">
         <v>69</v>
       </c>
       <c r="N8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1193,28 +1157,28 @@
         <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J9" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K9" t="s">
         <v>69</v>
       </c>
       <c r="L9" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="M9" t="s">
         <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1237,28 +1201,28 @@
         <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="K10" t="s">
         <v>69</v>
       </c>
       <c r="L10" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M10" t="s">
         <v>69</v>
       </c>
       <c r="N10" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1281,22 +1245,22 @@
         <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="K11" t="s">
         <v>69</v>
       </c>
       <c r="L11" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="M11" t="s">
         <v>69</v>
@@ -1325,28 +1289,28 @@
         <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="K12" t="s">
         <v>54</v>
       </c>
       <c r="L12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M12" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" t="s">
         <v>132</v>
-      </c>
-      <c r="M12" t="s">
-        <v>69</v>
-      </c>
-      <c r="N12" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1369,16 +1333,16 @@
         <v>66</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="J13" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s">
         <v>69</v>
@@ -1390,7 +1354,7 @@
         <v>69</v>
       </c>
       <c r="N13" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1413,28 +1377,28 @@
         <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H14" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="J14" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="K14" t="s">
         <v>54</v>
       </c>
       <c r="L14" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="M14" t="s">
         <v>69</v>
       </c>
       <c r="N14" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1457,28 +1421,28 @@
         <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K15" t="s">
         <v>54</v>
       </c>
       <c r="L15" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="M15" t="s">
         <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1501,16 +1465,16 @@
         <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I16" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="J16" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="K16" t="s">
         <v>69</v>
@@ -1522,7 +1486,7 @@
         <v>69</v>
       </c>
       <c r="N16" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
